--- a/order_generation/PO_excel/2EC.xlsx
+++ b/order_generation/PO_excel/2EC.xlsx
@@ -364,6 +364,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -389,6 +392,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -746,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -1021,7 +1027,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月23日</t>
+          <t>45天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1278,16 +1284,9 @@
     <row r="34" ht="21" customFormat="1" customHeight="1" s="6">
       <c r="H34" s="14" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="H38" s="14" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="12" t="n"/>
@@ -1388,7 +1387,6 @@
       <c r="A67" s="10" t="n"/>
       <c r="B67" s="12" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
@@ -1420,26 +1418,9 @@
       </c>
       <c r="F70" s="13" t="n"/>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="H80" s="14" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
